--- a/Result/profitability/1477.xlsx
+++ b/Result/profitability/1477.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>0.9</v>
       </c>
       <c r="M2" t="n">
-        <v>3.57</v>
+        <v>3.39</v>
       </c>
       <c r="N2" t="n">
-        <v>24.10375</v>
+        <v>24.1875</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.83</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08125</v>
+        <v>3.00375</v>
       </c>
       <c r="N3" t="n">
-        <v>23.35875</v>
+        <v>23.20875</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,10 +899,10 @@
         <v>1.08</v>
       </c>
       <c r="M4" t="n">
-        <v>2.72625</v>
+        <v>2.495</v>
       </c>
       <c r="N4" t="n">
-        <v>22.1325</v>
+        <v>21.70375</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>-0.79</v>
       </c>
       <c r="M5" t="n">
-        <v>1.98375</v>
+        <v>2.08375</v>
       </c>
       <c r="N5" t="n">
-        <v>20.2175</v>
+        <v>20.51</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1137,10 +1137,10 @@
         <v>1.29</v>
       </c>
       <c r="M6" t="n">
-        <v>1.8325</v>
+        <v>1.81</v>
       </c>
       <c r="N6" t="n">
-        <v>20.23625</v>
+        <v>20.48125</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1264,10 +1264,10 @@
         <v>1.37</v>
       </c>
       <c r="M7" t="n">
-        <v>1.56875</v>
+        <v>1.54125</v>
       </c>
       <c r="N7" t="n">
-        <v>20.29625</v>
+        <v>20.00125</v>
       </c>
       <c r="O7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>1.6</v>
       </c>
       <c r="M8" t="n">
-        <v>1.32875</v>
+        <v>1.1975</v>
       </c>
       <c r="N8" t="n">
-        <v>19.49125</v>
+        <v>19.27</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>1477</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>8166</v>
+      </c>
+      <c r="D75" t="n">
+        <v>6176</v>
+      </c>
+      <c r="E75" t="n">
+        <v>1990</v>
+      </c>
+      <c r="F75" t="n">
+        <v>24.37</v>
+      </c>
+      <c r="G75" t="n">
+        <v>1086</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>13.30%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>-15</v>
+      </c>
+      <c r="J75" t="n">
+        <v>1072</v>
+      </c>
+      <c r="K75" t="n">
+        <v>814</v>
+      </c>
+      <c r="L75" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M75" t="n">
+        <v>3.87</v>
+      </c>
+      <c r="N75" t="n">
+        <v>24.84375</v>
+      </c>
+      <c r="O75" t="n">
+        <v>0</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>0</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>0</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>1</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>-1.05</v>
+      </c>
+      <c r="X75" t="n">
+        <v>-0.2413793103448275</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-1.77</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.06771231828615143</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>0.7999999999999998</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>0.3199999999999998</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>2.34</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>0.106218792555606</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
